--- a/files/九龙-将军澳-凯柏峰 II.xlsx
+++ b/files/九龙-将军澳-凯柏峰 II.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8392,7 +8255,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8714,7 +8577,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -9036,7 +8899,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9358,7 +9221,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9680,7 +9543,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9772,7 +9635,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-03</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -10002,7 +9865,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10094,7 +9957,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10324,7 +10187,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10416,7 +10279,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10646,7 +10509,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10968,7 +10831,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11060,7 +10923,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11290,7 +11153,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11382,7 +11245,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11566,7 +11429,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11612,7 +11475,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -11704,7 +11567,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -11888,7 +11751,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -11934,7 +11797,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -12026,7 +11889,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12118,7 +11981,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12210,7 +12073,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12256,7 +12119,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12348,7 +12211,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12440,7 +12303,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12532,7 +12395,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12578,7 +12441,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12670,7 +12533,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -12762,7 +12625,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -12854,7 +12717,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -12900,7 +12763,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-26</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -12992,7 +12855,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -13084,7 +12947,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13176,7 +13039,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13222,7 +13085,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13314,7 +13177,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -13406,7 +13269,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13498,7 +13361,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -13544,7 +13407,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13636,7 +13499,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -13728,7 +13591,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -13820,7 +13683,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -13866,7 +13729,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -13958,7 +13821,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14050,7 +13913,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14142,7 +14005,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14188,7 +14051,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14280,7 +14143,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14464,7 +14327,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14510,7 +14373,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14786,7 +14649,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -14832,7 +14695,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -14924,7 +14787,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -15016,7 +14879,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15108,7 +14971,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -15154,7 +15017,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -15246,7 +15109,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -15338,7 +15201,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -15430,7 +15293,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -15476,7 +15339,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -15568,7 +15431,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -15660,7 +15523,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -15752,7 +15615,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -15798,7 +15661,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -15890,7 +15753,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -15982,7 +15845,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -16120,7 +15983,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -16304,7 +16167,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -23204,7 +23067,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -23388,7 +23251,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -23664,7 +23527,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -24216,7 +24079,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="H514" s="5" t="n">
@@ -24308,7 +24171,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -24584,7 +24447,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -24676,7 +24539,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -24768,7 +24631,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -24956,7 +24819,7 @@
       </c>
       <c r="G530" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="H530" s="5" t="n">
@@ -25048,7 +24911,7 @@
       </c>
       <c r="G532" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="H532" s="5" t="n">
@@ -25140,7 +25003,7 @@
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
@@ -25232,7 +25095,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -25324,7 +25187,7 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
@@ -25416,7 +25279,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -25508,7 +25371,7 @@
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="H542" s="5" t="n">
@@ -25600,7 +25463,7 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
@@ -25692,7 +25555,7 @@
       </c>
       <c r="G546" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H546" s="5" t="n">
@@ -25784,7 +25647,7 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
@@ -25968,7 +25831,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -26014,7 +25877,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -26152,7 +26015,7 @@
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H556" s="5" t="n">
@@ -26294,7 +26157,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -26340,7 +26203,7 @@
       </c>
       <c r="G560" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H560" s="5" t="n">
@@ -26432,7 +26295,7 @@
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H562" s="5" t="n">
@@ -26524,7 +26387,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -26570,7 +26433,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -26616,7 +26479,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -26708,7 +26571,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -26846,7 +26709,7 @@
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="H571" s="5" t="n">
@@ -26984,7 +26847,7 @@
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="H574" s="5" t="n">
@@ -27122,7 +26985,7 @@
       </c>
       <c r="G577" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H577" s="5" t="n">
@@ -27168,7 +27031,7 @@
       </c>
       <c r="G578" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H578" s="5" t="n">
@@ -27352,7 +27215,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -27398,7 +27261,7 @@
       </c>
       <c r="G583" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-27</t>
         </is>
       </c>
       <c r="H583" s="5" t="n">
@@ -27444,7 +27307,7 @@
       </c>
       <c r="G584" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H584" s="5" t="n">
@@ -27536,7 +27399,7 @@
       </c>
       <c r="G586" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H586" s="5" t="n">
@@ -27628,7 +27491,7 @@
       </c>
       <c r="G588" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H588" s="5" t="n">
@@ -27674,7 +27537,7 @@
       </c>
       <c r="G589" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H589" s="5" t="n">
@@ -27720,7 +27583,7 @@
       </c>
       <c r="G590" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H590" s="5" t="n">
@@ -27812,7 +27675,7 @@
       </c>
       <c r="G592" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H592" s="5" t="n">
@@ -27950,7 +27813,7 @@
       </c>
       <c r="G595" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="H595" s="5" t="n">
@@ -27996,7 +27859,7 @@
       </c>
       <c r="G596" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H596" s="5" t="n">
@@ -28226,7 +28089,7 @@
       </c>
       <c r="G601" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H601" s="5" t="n">
@@ -28364,7 +28227,7 @@
       </c>
       <c r="G604" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H604" s="5" t="n">
@@ -28456,7 +28319,7 @@
       </c>
       <c r="G606" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H606" s="5" t="n">
@@ -28502,7 +28365,7 @@
       </c>
       <c r="G607" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H607" s="5" t="n">
@@ -28548,7 +28411,7 @@
       </c>
       <c r="G608" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H608" s="5" t="n">
@@ -28640,7 +28503,7 @@
       </c>
       <c r="G610" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H610" s="5" t="n">
@@ -28732,7 +28595,7 @@
       </c>
       <c r="G612" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H612" s="5" t="n">
@@ -28778,7 +28641,7 @@
       </c>
       <c r="G613" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="H613" s="5" t="n">
@@ -28916,7 +28779,7 @@
       </c>
       <c r="G616" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="H616" s="5" t="n">
@@ -29008,7 +28871,7 @@
       </c>
       <c r="G618" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H618" s="5" t="n">
@@ -29054,7 +28917,7 @@
       </c>
       <c r="G619" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H619" s="5" t="n">
@@ -29100,7 +28963,7 @@
       </c>
       <c r="G620" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="H620" s="5" t="n">
@@ -29192,7 +29055,7 @@
       </c>
       <c r="G622" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H622" s="5" t="n">
@@ -29284,7 +29147,7 @@
       </c>
       <c r="G624" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H624" s="5" t="n">
@@ -29330,7 +29193,7 @@
       </c>
       <c r="G625" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H625" s="5" t="n">
@@ -29376,7 +29239,7 @@
       </c>
       <c r="G626" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H626" s="5" t="n">
@@ -29468,7 +29331,7 @@
       </c>
       <c r="G628" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H628" s="5" t="n">
@@ -29606,7 +29469,7 @@
       </c>
       <c r="G631" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H631" s="5" t="n">
@@ -29652,7 +29515,7 @@
       </c>
       <c r="G632" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H632" s="5" t="n">
@@ -29744,7 +29607,7 @@
       </c>
       <c r="G634" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H634" s="5" t="n">
@@ -29836,7 +29699,7 @@
       </c>
       <c r="G636" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H636" s="5" t="n">
@@ -29882,7 +29745,7 @@
       </c>
       <c r="G637" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H637" s="5" t="n">
@@ -29928,7 +29791,7 @@
       </c>
       <c r="G638" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H638" s="5" t="n">
@@ -30318,6138 +30181,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯柏峰 II - 2A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>348 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>347 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>67/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 892呎 (3房)
-$1,749万
-$19,604/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 317呎 (1房)
-$544万
-$17,159/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$576万
-$17,002/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 351呎 (1房)
-$593万
-$16,894/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 923呎 (3房)
-$1,882万
-$20,390/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>66/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$716万
-$16,158/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,313万
-$18,257/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$519万
-$15,267/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$513万
-$15,122/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$549万
-$15,560/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$785万
-$17,100/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$549万
-$15,829/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>65/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$715万
-$16,144/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,344万
-$18,698/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$518万
-$15,245/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$512万
-$15,109/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$549万
-$15,543/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$776万
-$16,915/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$517万
-$14,893/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>63/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$714万
-$16,126/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,310万
-$18,221/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$518万
-$15,222/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$512万
-$15,092/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$548万
-$15,526/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$776万
-$16,898/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$548万
-$15,752/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$714万
-$16,111/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,283万
-$17,847/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$517万
-$15,199/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$511万
-$15,076/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$547万
-$15,509/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$775万
-$16,880/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$548万
-$15,782/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$713万
-$16,093/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,282万
-$17,828/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$516万
-$15,176/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$511万
-$15,061/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$547万
-$15,495/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$774万
-$16,863/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$547万
-$15,765/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$712万
-$16,079/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,281万
-$17,811/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$515万
-$15,154/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$510万
-$15,049/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$546万
-$15,480/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$773万
-$16,845/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$547万
-$15,750/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$712万
-$16,061/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,267万
-$17,616/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$514万
-$15,131/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$510万
-$15,031/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$546万
-$15,463/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$772万
-$16,791/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$545万
-$15,718/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$712万
-$16,061/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$514万
-$15,131/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$510万
-$15,031/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$546万
-$15,463/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$772万
-$16,828/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$545万
-$15,718/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$710万
-$16,029/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,277万
-$17,757/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$513万
-$15,088/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$509万
-$15,003/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$545万
-$15,434/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$763万
-$16,627/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$544万
-$15,688/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$709万
-$16,014/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,275万
-$17,739/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$512万
-$15,065/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$508万
-$14,988/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$544万
-$15,416/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$762万
-$16,610/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$544万
-$15,626/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$709万
-$15,998/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,274万
-$17,722/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$511万
-$15,042/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$507万
-$14,970/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$544万
-$15,402/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$762万
-$16,595/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$543万
-$15,611/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$715万
-$16,142/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,273万
-$17,702/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$511万
-$15,019/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$507万
-$14,957/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$543万
-$15,387/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$761万
-$16,580/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$543万
-$15,641/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$714万
-$16,124/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,259万
-$17,512/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$510万
-$14,997/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$507万
-$14,942/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$543万
-$15,370/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$760万
-$16,564/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$542万
-$15,624/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$714万
-$16,111/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,258万
-$17,494/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$509万
-$14,974/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$506万
-$14,929/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$542万
-$15,356/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$760万
-$16,547/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$542万
-$15,564/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$706万
-$15,935/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,256万
-$17,474/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$508万
-$14,951/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$506万
-$14,914/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$542万
-$15,343/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$759万
-$16,529/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$541万
-$15,549/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>49/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$712万
-$16,077/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,293万
-$17,986/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$508万
-$14,946/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$505万
-$14,906/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$541万
-$15,329/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$758万
-$16,512/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$540万
-$15,562/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$705万
-$15,916/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,293万
-$17,986/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$508万
-$14,946/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$505万
-$14,906/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$541万
-$15,329/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$758万
-$16,512/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$540万
-$15,562/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$711万
-$16,045/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,265万
-$17,598/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$508万
-$14,939/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$505万
-$14,896/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$540万
-$15,297/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$756万
-$16,481/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$539万
-$15,485/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$703万
-$15,869/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,264万
-$17,580/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$508万
-$14,936/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$505万
-$14,891/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$539万
-$15,282/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$756万
-$16,464/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$538万
-$15,515/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$702万
-$15,856/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,263万
-$17,563/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$508万
-$14,934/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$505万
-$14,886/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$539万
-$15,265/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$755万
-$16,449/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$538万
-$15,500/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$702万
-$15,837/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,249万
-$17,371/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$508万
-$14,931/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$504万
-$14,881/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$538万
-$15,251/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$754万
-$16,431/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$537万
-$15,482/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$701万
-$15,824/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,248万
-$17,353/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$507万
-$14,924/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$504万
-$14,879/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$538万
-$15,236/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$753万
-$16,412/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$537万
-$15,470/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$700万
-$15,806/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,246万
-$17,337/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$507万
-$14,921/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$504万
-$14,871/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$537万
-$15,219/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$753万
-$16,399/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$536万
-$15,411/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$699万
-$15,777/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,256万
-$17,474/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$507万
-$14,913/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$504万
-$14,861/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$544万
-$15,416/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$904万
-$19,686/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$535万
-$15,423/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$699万
-$15,777/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,256万
-$17,474/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$507万
-$14,913/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$504万
-$14,861/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$544万
-$15,416/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$904万
-$19,686/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$535万
-$15,423/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$704万
-$15,903/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,252万
-$17,406/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$507万
-$14,908/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$503万
-$14,848/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$543万
-$15,387/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$854万
-$18,610/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$534万
-$15,391/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$697万
-$15,729/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,249万
-$17,371/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$507万
-$14,901/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$503万
-$14,846/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$543万
-$15,370/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$853万
-$18,573/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$534万
-$15,376/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$696万
-$15,711/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,246万
-$17,337/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$507万
-$14,898/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$664万
-$19,592/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$542万
-$15,356/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$851万
-$18,537/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$533万
-$15,317/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$695万
-$15,698/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,232万
-$17,131/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$506万
-$14,896/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$663万
-$19,555/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$542万
-$15,341/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$895万
-$19,489/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$533万
-$15,346/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$695万
-$15,682/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,229万
-$17,097/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$506万
-$14,891/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$697万
-$20,558/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$541万
-$15,324/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$847万
-$18,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$532万
-$15,329/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$694万
-$15,664/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,239万
-$17,234/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$506万
-$14,888/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$696万
-$20,519/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$540万
-$15,309/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$891万
-$19,412/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$531万
-$15,272/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$693万
-$15,650/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,224万
-$17,028/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$506万
-$14,886/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$694万
-$20,478/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$540万
-$15,295/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>F | 460呎 (2房)
-$889万
-$19,331/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$531万
-$15,257/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$692万
-$15,619/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,222万
-$16,993/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$506万
-$14,878/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$693万
-$20,438/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$539万
-$15,278/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$842万
-$18,350/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$530万
-$15,269/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$692万
-$15,619/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,222万
-$16,993/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$506万
-$14,878/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$693万
-$20,438/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$539万
-$15,278/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$887万
-$19,333/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$724万
-$20,870/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$689万
-$15,555/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,288万
-$17,911/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$506万
-$14,873/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$690万
-$20,358/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$539万
-$15,270/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$884万
-$19,256/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H41" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$721万
-$20,786/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$688万
-$15,526/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,354万
-$18,832/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$506万
-$14,870/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$689万
-$20,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$539万
-$15,263/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$882万
-$19,219/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H42" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$720万
-$20,748/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$686万
-$15,494/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,351万
-$18,794/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$505万
-$14,865/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$687万
-$20,276/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$539万
-$15,256/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$836万
-$18,205/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H43" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$718万
-$20,704/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$685万
-$15,463/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,349万
-$18,757/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$505万
-$14,863/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$686万
-$20,232/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$538万
-$15,251/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$879万
-$19,140/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$717万
-$20,661/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$684万
-$15,431/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,346万
-$18,719/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$505万
-$14,860/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$685万
-$20,193/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$538万
-$15,248/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$877万
-$19,103/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$716万
-$20,623/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$682万
-$15,400/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,275万
-$17,733/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$505万
-$14,853/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$683万
-$20,154/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$538万
-$15,241/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$875万
-$19,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (1房)
-$678万
-$19,477/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$681万
-$15,372/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,341万
-$18,645/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$505万
-$14,850/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$647万
-$19,092/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$538万
-$15,236/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$873万
-$19,026/呎
-(22年-07月)</t>
-        </is>
-      </c>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$677万
-$19,497/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$690万
-$15,569/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,224万
-$17,026/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$505万
-$14,848/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$680万
-$20,073/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$538万
-$15,229/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$827万
-$18,024/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H48" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$675万
-$19,455/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$690万
-$15,569/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,224万
-$17,026/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$505万
-$14,848/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$680万
-$20,073/呎
-(22年-07月)</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$538万
-$15,229/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$872万
-$18,990/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$675万
-$19,455/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$687万
-$15,510/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,333万
-$18,533/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$505万
-$14,842/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$678万
-$19,992/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$537万
-$15,219/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$868万
-$18,915/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$708万
-$20,416/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$686万
-$15,476/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,330万
-$18,496/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$505万
-$14,840/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$676万
-$19,953/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$537万
-$15,214/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$866万
-$18,876/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$707万
-$20,375/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="65" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$684万
-$15,447/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,327万
-$18,461/呎
-(22年-07月)</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$504万
-$14,835/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$675万
-$19,911/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$537万
-$15,207/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$865万
-$18,837/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H52" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$706万
-$20,337/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="65" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$683万
-$15,418/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,280万
-$17,799/呎
-(22年-07月)</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$522万
-$15,351/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$674万
-$19,872/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$537万
-$15,202/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$863万
-$18,801/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H53" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$704万
-$20,294/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="65" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$687万
-$15,506/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>B | 719呎 (3房)
-$1,319万
-$18,350/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>C | 340呎 (1房)
-$504万
-$14,825/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>D | 339呎 (1房)
-$671万
-$19,794/呎
-(23年-07月)</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>E | 353呎 (1房)
-$536万
-$15,197/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$860万
-$18,726/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H54" s="16" t="inlineStr">
-        <is>
-          <t>G | 347呎 (1房)
-$527万
-$15,180/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="65" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>A | 405呎 (2房)
-$715万
-$17,654/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>B | 678呎 (3房)
-$1,275万
-$18,810/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>C | 302呎 (1房)
-$471万
-$15,597/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>D | 301呎 (1房)
-$467万
-$15,511/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>E | 315呎 (1房)
-$504万
-$16,004/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>F | 422呎 (2房)
-$739万
-$17,518/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H55" s="16" t="inlineStr">
-        <is>
-          <t>G | 309呎 (1房)
-$558万
-$18,051/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯柏峰 II - 2B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>296 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>294 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>67/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 891呎 (3房)
-$1,760万
-$19,747/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 904呎 (3房)
-$1,724万
-$19,076/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>66/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$739万
-$16,026/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$520万
-$15,439/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$748万
-$16,166/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$900万
-$17,622/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$770万
-$16,991/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$819万
-$18,162/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>65/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$738万
-$16,011/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$520万
-$15,426/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$748万
-$16,151/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$891万
-$17,431/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$769万
-$16,976/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$822万
-$18,235/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>63/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$737万
-$15,993/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$519万
-$15,411/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$743万
-$16,054/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$864万
-$16,908/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$768万
-$16,958/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$786万
-$17,421/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$737万
-$15,978/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$519万
-$15,398/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$743万
-$16,039/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$863万
-$16,890/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$768万
-$16,943/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$888万
-$19,694/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$736万
-$15,961/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$518万
-$15,385/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$734万
-$15,862/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$850万
-$16,624/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$774万
-$17,093/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$776万
-$17,213/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$735万
-$15,948/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$518万
-$15,375/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$734万
-$15,849/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$849万
-$16,609/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$766万
-$16,907/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$776万
-$17,197/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$734万
-$15,931/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$518万
-$15,363/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$733万
-$15,832/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$909万
-$17,781/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$773万
-$17,060/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$775万
-$17,180/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$734万
-$15,931/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$518万
-$15,363/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$737万
-$15,911/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$909万
-$17,781/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$773万
-$17,060/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$782万
-$17,350/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$733万
-$15,898/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$517万
-$15,337/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$735万
-$15,881/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$889万
-$17,395/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$764万
-$16,857/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$773万
-$17,142/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$732万
-$15,883/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$516万
-$15,324/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$734万
-$15,864/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$845万
-$16,540/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$763万
-$16,839/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$765万
-$16,960/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$731万
-$15,866/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$516万
-$15,314/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$734万
-$15,849/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$844万
-$16,524/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$762万
-$16,823/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$776万
-$17,197/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$731万
-$15,852/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$516万
-$15,301/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$730万
-$15,758/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$844万
-$16,507/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$761万
-$16,808/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$771万
-$17,093/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$730万
-$15,833/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$515万
-$15,288/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$722万
-$15,583/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$843万
-$16,491/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$760万
-$16,788/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$770万
-$17,075/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$729万
-$15,818/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$515万
-$15,276/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$721万
-$15,570/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$842万
-$16,474/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$752万
-$16,607/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$762万
-$16,889/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$729万
-$15,805/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$514万
-$15,263/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$720万
-$15,551/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$841万
-$16,460/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$752万
-$16,589/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$761万
-$16,871/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>49/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$728万
-$15,787/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$514万
-$15,253/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$723万
-$15,616/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$832万
-$16,278/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$751万
-$16,572/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$760万
-$16,858/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$728万
-$15,787/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$514万
-$15,253/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$723万
-$15,616/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$832万
-$16,280/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$758万
-$16,740/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$760万
-$16,858/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$726万
-$15,755/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$513万
-$15,227/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$722万
-$15,585/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$830万
-$16,247/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$757万
-$16,709/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$759万
-$16,823/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$726万
-$15,740/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$513万
-$15,215/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$721万
-$15,568/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$863万
-$16,886/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$749万
-$16,525/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$758万
-$16,805/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$725万
-$15,725/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$512万
-$15,204/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$716万
-$15,475/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$854万
-$16,705/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$748万
-$16,508/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$757万
-$16,787/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$724万
-$15,709/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$512万
-$15,191/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$716万
-$15,458/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$853万
-$16,687/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$747万
-$16,490/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$768万
-$17,024/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$724万
-$15,694/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$512万
-$15,179/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$715万
-$15,445/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$835万
-$16,344/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$746万
-$16,472/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$767万
-$17,007/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$770万
-$16,696/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$511万
-$15,166/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$718万
-$15,505/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$834万
-$16,327/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$746万
-$16,459/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$770万
-$17,075/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$914万
-$19,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$511万
-$15,156/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$724万
-$15,629/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$824万
-$16,133/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$846万
-$18,684/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$752万
-$16,672/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$868万
-$18,824/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$511万
-$15,156/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$724万
-$15,629/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$824万
-$16,133/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$743万
-$16,393/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$752万
-$16,672/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$724万
-$15,694/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$510万
-$15,140/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$722万
-$15,598/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$823万
-$16,100/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$740万
-$16,329/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$749万
-$16,605/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$864万
-$18,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$510万
-$15,133/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$721万
-$15,581/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$855万
-$16,736/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$738万
-$16,294/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$747万
-$16,572/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$722万
-$15,662/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$510万
-$15,125/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$721万
-$15,568/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$854万
-$16,718/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$885万
-$19,526/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$746万
-$16,539/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$877万
-$19,018/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$509万
-$15,118/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$899万
-$19,413/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$845万
-$16,538/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$838万
-$18,498/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$752万
-$16,672/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$906万
-$19,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$509万
-$15,112/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$898万
-$19,386/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$844万
-$16,521/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$750万
-$16,641/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$859万
-$18,628/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$509万
-$15,102/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$851万
-$18,371/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$843万
-$16,505/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$835万
-$18,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$749万
-$16,605/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$903万
-$19,597/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$509万
-$15,095/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$849万
-$18,344/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$818万
-$16,008/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$878万
-$19,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$744万
-$16,488/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$854万
-$18,527/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$509万
-$15,089/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$893万
-$19,296/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$816万
-$15,975/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$876万
-$19,333/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$742万
-$16,457/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$902万
-$19,568/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$509万
-$15,089/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$836万
-$18,045/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$940万
-$18,398/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$876万
-$19,333/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$742万
-$16,457/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$899万
-$19,508/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$508万
-$15,072/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$845万
-$18,260/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$987万
-$19,307/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F41" s="19" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$739万
-$16,392/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$898万
-$19,478/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$508万
-$15,066/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$889万
-$19,210/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$985万
-$19,267/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$871万
-$19,218/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$738万
-$16,357/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$851万
-$18,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$507万
-$15,056/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$879万
-$18,994/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$933万
-$18,250/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$892万
-$19,689/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$733万
-$16,244/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$833万
-$18,069/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$507万
-$15,049/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$887万
-$19,153/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$981万
-$19,191/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$890万
-$19,649/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$731万
-$16,211/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$894万
-$19,391/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$507万
-$15,044/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$885万
-$19,124/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$979万
-$19,151/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$865万
-$19,105/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$730万
-$16,180/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$847万
-$18,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$507万
-$15,033/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$839万
-$18,124/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$977万
-$19,115/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$864万
-$19,064/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$728万
-$16,146/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$857万
-$18,597/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$506万
-$15,028/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$883万
-$19,067/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$975万
-$19,075/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$885万
-$19,530/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$727万
-$16,115/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$890万
-$19,305/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$506万
-$15,020/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$825万
-$17,827/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$923万
-$18,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$840万
-$18,554/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$733万
-$16,244/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$845万
-$18,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$506万
-$15,020/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$882万
-$19,040/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$973万
-$19,039/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$816万
-$18,024/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$733万
-$16,244/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$887万
-$19,247/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$506万
-$15,005/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$824万
-$17,786/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$966万
-$18,911/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$857万
-$18,913/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$730万
-$16,180/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$841万
-$18,241/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$505万
-$14,998/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$833万
-$17,988/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$964万
-$18,872/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$855万
-$18,876/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$728万
-$16,146/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="65" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$885万
-$19,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$505万
-$14,987/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$832万
-$17,963/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$961万
-$18,803/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$853万
-$18,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$727万
-$16,115/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="65" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$838万
-$18,187/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$505万
-$14,982/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$875万
-$18,897/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$959万
-$18,767/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$812万
-$17,927/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$725万
-$16,082/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="65" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>A | 461呎 (2房)
-$823万
-$17,857/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>B | 337呎 (1房)
-$505万
-$14,974/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$872万
-$18,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$948万
-$18,545/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$799万
-$17,640/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>F | 451呎 (2房)
-$737万
-$16,339/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="65" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>A | 423呎 (2房)
-$759万
-$17,940/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>B | 299呎 (1房)
-$516万
-$17,269/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>C | 425呎 (2房)
-$754万
-$17,730/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>D | 511呎 (2房)
-$949万
-$18,579/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>E | 415呎 (2房)
-$745万
-$17,954/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>F | 413呎 (2房)
-$753万
-$18,224/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-将军澳-凯柏峰 II.xlsx
+++ b/files/九龙-将军澳-凯柏峰 II.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +143,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +224,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -30181,4 +30361,6138 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 892呎 (3房)
+$1749万
+$19,604/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 317呎 (1房)
+$544万
+$17,159/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$576万
+$17,002/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 351呎 (1房)
+$593万
+$16,894/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 923呎 (3房)
+$1882万
+$20,390/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$716万
+$16,158/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1313万
+$18,257/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$519万
+$15,267/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$513万
+$15,122/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$549万
+$15,560/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$785万
+$17,100/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$549万
+$15,829/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$715万
+$16,144/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1344万
+$18,698/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$518万
+$15,245/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$512万
+$15,109/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$549万
+$15,543/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$776万
+$16,915/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$517万
+$14,893/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$714万
+$16,126/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1310万
+$18,221/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$518万
+$15,222/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$512万
+$15,092/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$548万
+$15,526/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$776万
+$16,898/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$548万
+$15,752/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$714万
+$16,111/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1283万
+$17,847/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$517万
+$15,199/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$511万
+$15,076/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$547万
+$15,509/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$775万
+$16,880/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$548万
+$15,782/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$713万
+$16,093/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1282万
+$17,828/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$516万
+$15,176/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$511万
+$15,061/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$547万
+$15,495/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$774万
+$16,863/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$547万
+$15,765/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$712万
+$16,079/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1281万
+$17,811/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$515万
+$15,154/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$510万
+$15,049/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$546万
+$15,480/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$773万
+$16,845/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$547万
+$15,750/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$712万
+$16,061/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1267万
+$17,616/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$514万
+$15,131/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$510万
+$15,031/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$546万
+$15,463/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+$772万
+$16,791/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$545万
+$15,718/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$712万
+$16,061/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$514万
+$15,131/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$510万
+$15,031/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$546万
+$15,463/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$772万
+$16,828/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$545万
+$15,718/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$710万
+$16,029/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1277万
+$17,757/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$513万
+$15,088/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$509万
+$15,003/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$545万
+$15,434/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$763万
+$16,627/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$544万
+$15,688/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$709万
+$16,014/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1275万
+$17,739/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$512万
+$15,065/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$508万
+$14,988/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$544万
+$15,416/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$762万
+$16,610/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$544万
+$15,626/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$709万
+$15,998/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1274万
+$17,722/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$511万
+$15,042/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$507万
+$14,970/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$544万
+$15,402/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$762万
+$16,595/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$543万
+$15,611/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$715万
+$16,142/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1273万
+$17,702/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$511万
+$15,019/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$507万
+$14,957/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$543万
+$15,387/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$761万
+$16,580/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$543万
+$15,641/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$714万
+$16,124/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1259万
+$17,512/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$510万
+$14,997/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$507万
+$14,942/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$543万
+$15,370/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$760万
+$16,564/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$542万
+$15,624/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$714万
+$16,111/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1258万
+$17,494/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$509万
+$14,974/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$506万
+$14,929/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$542万
+$15,356/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$760万
+$16,547/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$542万
+$15,564/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$706万
+$15,935/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1256万
+$17,474/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$508万
+$14,951/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$506万
+$14,914/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$542万
+$15,343/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$759万
+$16,529/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$541万
+$15,549/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$712万
+$16,077/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1293万
+$17,986/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$508万
+$14,946/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$505万
+$14,906/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$541万
+$15,329/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$758万
+$16,512/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$540万
+$15,562/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$705万
+$15,916/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1293万
+$17,986/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$508万
+$14,946/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$505万
+$14,906/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$541万
+$15,329/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$758万
+$16,512/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$540万
+$15,562/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$711万
+$16,045/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1265万
+$17,598/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$508万
+$14,939/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$505万
+$14,896/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$540万
+$15,297/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$756万
+$16,481/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$539万
+$15,485/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$703万
+$15,869/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1264万
+$17,580/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$508万
+$14,936/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$505万
+$14,891/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$539万
+$15,282/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$756万
+$16,464/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$538万
+$15,515/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$702万
+$15,856/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1263万
+$17,563/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$508万
+$14,934/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$505万
+$14,886/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$539万
+$15,265/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$755万
+$16,449/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$538万
+$15,500/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$702万
+$15,837/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1249万
+$17,371/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$508万
+$14,931/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$504万
+$14,881/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$538万
+$15,251/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$754万
+$16,431/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$537万
+$15,482/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$701万
+$15,824/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1248万
+$17,353/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$507万
+$14,924/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$504万
+$14,879/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$538万
+$15,236/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$753万
+$16,412/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$537万
+$15,470/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$700万
+$15,806/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1246万
+$17,337/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$507万
+$14,921/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$504万
+$14,871/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$537万
+$15,219/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$753万
+$16,399/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$536万
+$15,411/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$699万
+$15,777/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1256万
+$17,474/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$507万
+$14,913/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$504万
+$14,861/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$544万
+$15,416/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$904万
+$19,686/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$535万
+$15,423/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$699万
+$15,777/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1256万
+$17,474/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$507万
+$14,913/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$504万
+$14,861/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$544万
+$15,416/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$904万
+$19,686/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$535万
+$15,423/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$704万
+$15,903/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1252万
+$17,406/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$507万
+$14,908/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$503万
+$14,848/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$543万
+$15,387/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$854万
+$18,610/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$534万
+$15,391/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$697万
+$15,729/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1249万
+$17,371/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$507万
+$14,901/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$503万
+$14,846/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$543万
+$15,370/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$853万
+$18,573/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$534万
+$15,376/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$696万
+$15,711/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1246万
+$17,337/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$507万
+$14,898/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$664万
+$19,592/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$542万
+$15,356/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$851万
+$18,537/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$533万
+$15,317/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$695万
+$15,698/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1232万
+$17,131/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$506万
+$14,896/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$663万
+$19,555/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$542万
+$15,341/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$895万
+$19,489/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$533万
+$15,346/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$695万
+$15,682/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1229万
+$17,097/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$506万
+$14,891/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$697万
+$20,558/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$541万
+$15,324/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$847万
+$18,462/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$532万
+$15,329/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$694万
+$15,664/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1239万
+$17,234/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$506万
+$14,888/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$696万
+$20,519/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$540万
+$15,309/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$891万
+$19,412/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$531万
+$15,272/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$693万
+$15,650/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1224万
+$17,028/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$506万
+$14,886/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$694万
+$20,478/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$540万
+$15,295/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>F | 460呎 (2房)
+$889万
+$19,331/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$531万
+$15,257/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$692万
+$15,619/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1222万
+$16,993/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$506万
+$14,878/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$693万
+$20,438/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$539万
+$15,278/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$842万
+$18,350/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$530万
+$15,269/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$692万
+$15,619/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1222万
+$16,993/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$506万
+$14,878/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$693万
+$20,438/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$539万
+$15,278/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$887万
+$19,333/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$724万
+$20,870/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$689万
+$15,555/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1288万
+$17,911/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$506万
+$14,873/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$690万
+$20,358/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$539万
+$15,270/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$884万
+$19,256/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$721万
+$20,786/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$688万
+$15,526/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1354万
+$18,832/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$506万
+$14,870/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$689万
+$20,316/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$539万
+$15,263/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$882万
+$19,219/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$720万
+$20,748/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$686万
+$15,494/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1351万
+$18,794/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$505万
+$14,865/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$687万
+$20,276/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$539万
+$15,256/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$836万
+$18,205/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$718万
+$20,704/呎
+(22年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$685万
+$15,463/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1349万
+$18,757/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$505万
+$14,863/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$686万
+$20,232/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$538万
+$15,251/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$879万
+$19,140/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$717万
+$20,661/呎
+(22年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$684万
+$15,431/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1346万
+$18,719/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$505万
+$14,860/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$685万
+$20,193/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$538万
+$15,248/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$877万
+$19,103/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$716万
+$20,623/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$682万
+$15,400/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1275万
+$17,733/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$505万
+$14,853/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$683万
+$20,154/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$538万
+$15,241/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$875万
+$19,065/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (1房)
+$678万
+$19,477/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$681万
+$15,372/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1341万
+$18,645/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$505万
+$14,850/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$647万
+$19,092/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$538万
+$15,236/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$873万
+$19,026/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$677万
+$19,497/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$690万
+$15,569/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1224万
+$17,026/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$505万
+$14,848/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$680万
+$20,073/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$538万
+$15,229/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$827万
+$18,024/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$675万
+$19,455/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$690万
+$15,569/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1224万
+$17,026/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$505万
+$14,848/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$680万
+$20,073/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$538万
+$15,229/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$872万
+$18,990/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$675万
+$19,455/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$687万
+$15,510/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1333万
+$18,533/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$505万
+$14,842/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$678万
+$19,992/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$537万
+$15,219/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$868万
+$18,915/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$708万
+$20,416/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$686万
+$15,476/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1330万
+$18,496/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$505万
+$14,840/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$676万
+$19,953/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$537万
+$15,214/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$866万
+$18,876/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H50" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$707万
+$20,375/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$684万
+$15,447/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1327万
+$18,461/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$504万
+$14,835/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$675万
+$19,911/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$537万
+$15,207/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$865万
+$18,837/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$706万
+$20,337/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$683万
+$15,418/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1280万
+$17,799/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$522万
+$15,351/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$674万
+$19,872/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$537万
+$15,202/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$863万
+$18,801/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$704万
+$20,294/呎
+(22年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$687万
+$15,506/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>B | 719呎 (3房)
+$1319万
+$18,350/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>C | 340呎 (1房)
+$504万
+$14,825/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>D | 339呎 (1房)
+$671万
+$19,794/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>E | 353呎 (1房)
+$536万
+$15,197/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$860万
+$18,726/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>G | 347呎 (1房)
+$527万
+$15,180/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>A | 405呎 (2房)
+$715万
+$17,654/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>B | 678呎 (3房)
+$1275万
+$18,810/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>C | 302呎 (1房)
+$471万
+$15,597/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>D | 301呎 (1房)
+$467万
+$15,511/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>E | 315呎 (1房)
+$504万
+$16,004/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>F | 422呎 (2房)
+$739万
+$17,518/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>G | 309呎 (1房)
+$558万
+$18,051/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 891呎 (3房)
+$1760万
+$19,747/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 904呎 (3房)
+$1724万
+$19,076/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$739万
+$16,026/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$520万
+$15,439/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$748万
+$16,166/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$900万
+$17,622/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$770万
+$16,991/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$819万
+$18,162/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$738万
+$16,011/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$520万
+$15,426/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$748万
+$16,151/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$891万
+$17,431/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$769万
+$16,976/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$822万
+$18,235/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$737万
+$15,993/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$519万
+$15,411/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$743万
+$16,054/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$864万
+$16,908/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$768万
+$16,958/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$786万
+$17,421/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$737万
+$15,978/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$519万
+$15,398/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$743万
+$16,039/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$863万
+$16,890/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$768万
+$16,943/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$888万
+$19,694/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$736万
+$15,961/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$518万
+$15,385/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$734万
+$15,862/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$850万
+$16,624/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$774万
+$17,093/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$776万
+$17,213/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$735万
+$15,948/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$518万
+$15,375/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$734万
+$15,849/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$849万
+$16,609/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$766万
+$16,907/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$776万
+$17,197/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$734万
+$15,931/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$518万
+$15,363/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$733万
+$15,832/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$909万
+$17,781/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$773万
+$17,060/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$775万
+$17,180/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$734万
+$15,931/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$518万
+$15,363/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$737万
+$15,911/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$909万
+$17,781/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$773万
+$17,060/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$782万
+$17,350/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$733万
+$15,898/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$517万
+$15,337/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$735万
+$15,881/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$889万
+$17,395/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$764万
+$16,857/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$773万
+$17,142/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$732万
+$15,883/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$516万
+$15,324/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$734万
+$15,864/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$845万
+$16,540/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$763万
+$16,839/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$765万
+$16,960/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$731万
+$15,866/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$516万
+$15,314/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$734万
+$15,849/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$844万
+$16,524/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$762万
+$16,823/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$776万
+$17,197/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$731万
+$15,852/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$516万
+$15,301/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$730万
+$15,758/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$844万
+$16,507/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$761万
+$16,808/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$771万
+$17,093/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$730万
+$15,833/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$515万
+$15,288/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$722万
+$15,583/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$843万
+$16,491/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$760万
+$16,788/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$770万
+$17,075/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$729万
+$15,818/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$515万
+$15,276/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$721万
+$15,570/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$842万
+$16,474/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$752万
+$16,607/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$762万
+$16,889/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$729万
+$15,805/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$514万
+$15,263/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$720万
+$15,551/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$841万
+$16,460/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$752万
+$16,589/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$761万
+$16,871/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$728万
+$15,787/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$514万
+$15,253/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$723万
+$15,616/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$832万
+$16,278/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$751万
+$16,572/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$760万
+$16,858/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$728万
+$15,787/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$514万
+$15,253/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$723万
+$15,616/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$832万
+$16,280/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$758万
+$16,740/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$760万
+$16,858/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$726万
+$15,755/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$513万
+$15,227/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$722万
+$15,585/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$830万
+$16,247/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$757万
+$16,709/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$759万
+$16,823/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$726万
+$15,740/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$513万
+$15,215/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$721万
+$15,568/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$863万
+$16,886/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$749万
+$16,525/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$758万
+$16,805/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$725万
+$15,725/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$512万
+$15,204/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$716万
+$15,475/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$854万
+$16,705/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$748万
+$16,508/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$757万
+$16,787/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$724万
+$15,709/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$512万
+$15,191/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$716万
+$15,458/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$853万
+$16,687/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$747万
+$16,490/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$768万
+$17,024/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$724万
+$15,694/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$512万
+$15,179/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$715万
+$15,445/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$835万
+$16,344/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$746万
+$16,472/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$767万
+$17,007/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$770万
+$16,696/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$511万
+$15,166/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$718万
+$15,505/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$834万
+$16,327/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$746万
+$16,459/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$770万
+$17,075/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$914万
+$19,833/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$511万
+$15,156/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$724万
+$15,629/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$824万
+$16,133/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$846万
+$18,684/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$752万
+$16,672/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$868万
+$18,824/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$511万
+$15,156/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$724万
+$15,629/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$824万
+$16,133/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$743万
+$16,393/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$752万
+$16,672/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$724万
+$15,694/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$510万
+$15,140/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$722万
+$15,598/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$823万
+$16,100/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$740万
+$16,329/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$749万
+$16,605/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$864万
+$18,741/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$510万
+$15,133/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$721万
+$15,581/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$855万
+$16,736/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$738万
+$16,294/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$747万
+$16,572/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$722万
+$15,662/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$510万
+$15,125/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$721万
+$15,568/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$854万
+$16,718/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$885万
+$19,526/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$746万
+$16,539/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$877万
+$19,018/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$509万
+$15,118/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$899万
+$19,413/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$845万
+$16,538/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$838万
+$18,498/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$752万
+$16,672/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$906万
+$19,654/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$509万
+$15,112/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$898万
+$19,386/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$844万
+$16,521/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$750万
+$16,641/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$859万
+$18,628/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$509万
+$15,102/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$851万
+$18,371/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$843万
+$16,505/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$835万
+$18,424/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$749万
+$16,605/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$903万
+$19,597/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$509万
+$15,095/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$849万
+$18,344/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$818万
+$16,008/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$878万
+$19,374/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$744万
+$16,488/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$854万
+$18,527/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$509万
+$15,089/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$893万
+$19,296/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$816万
+$15,975/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$876万
+$19,333/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$742万
+$16,457/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$902万
+$19,568/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$509万
+$15,089/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$836万
+$18,045/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$940万
+$18,398/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$876万
+$19,333/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$742万
+$16,457/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$899万
+$19,508/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$508万
+$15,072/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$845万
+$18,260/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$987万
+$19,307/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$739万
+$16,392/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$898万
+$19,478/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$508万
+$15,066/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$889万
+$19,210/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$985万
+$19,267/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$871万
+$19,218/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$738万
+$16,357/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$851万
+$18,462/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$507万
+$15,056/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$879万
+$18,994/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$933万
+$18,250/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$892万
+$19,689/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$733万
+$16,244/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$833万
+$18,069/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$507万
+$15,049/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$887万
+$19,153/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$981万
+$19,191/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$890万
+$19,649/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$731万
+$16,211/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$894万
+$19,391/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$507万
+$15,044/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$885万
+$19,124/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$979万
+$19,151/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$865万
+$19,105/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$730万
+$16,180/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$847万
+$18,378/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$507万
+$15,033/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$839万
+$18,124/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$977万
+$19,115/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$864万
+$19,064/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$728万
+$16,146/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$857万
+$18,597/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$506万
+$15,028/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$883万
+$19,067/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$975万
+$19,075/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$885万
+$19,530/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$727万
+$16,115/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$890万
+$19,305/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$506万
+$15,020/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$825万
+$17,827/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$923万
+$18,071/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$840万
+$18,554/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$733万
+$16,244/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$845万
+$18,323/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$506万
+$15,020/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$882万
+$19,040/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$973万
+$19,039/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$816万
+$18,024/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$733万
+$16,244/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$887万
+$19,247/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$506万
+$15,005/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$824万
+$17,786/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$966万
+$18,911/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$857万
+$18,913/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$730万
+$16,180/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$841万
+$18,241/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$505万
+$14,998/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$833万
+$17,988/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$964万
+$18,872/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$855万
+$18,876/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$728万
+$16,146/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$885万
+$19,190/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$505万
+$14,987/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$832万
+$17,963/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$961万
+$18,803/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$853万
+$18,839/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$727万
+$16,115/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$838万
+$18,187/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$505万
+$14,982/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$875万
+$18,897/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$959万
+$18,767/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$812万
+$17,927/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$725万
+$16,082/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>A | 461呎 (2房)
+$823万
+$17,857/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>B | 337呎 (1房)
+$505万
+$14,974/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$872万
+$18,839/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$948万
+$18,545/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$799万
+$17,640/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>F | 451呎 (2房)
+$737万
+$16,339/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>A | 423呎 (2房)
+$759万
+$17,940/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>B | 299呎 (1房)
+$516万
+$17,269/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>C | 425呎 (2房)
+$754万
+$17,730/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>D | 511呎 (2房)
+$949万
+$18,579/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>E | 415呎 (2房)
+$745万
+$17,954/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>F | 413呎 (2房)
+$753万
+$18,224/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-将军澳-凯柏峰 II.xlsx
+++ b/files/九龙-将军澳-凯柏峰 II.xlsx
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
